--- a/Data/PERMANOVA_data.xlsx
+++ b/Data/PERMANOVA_data.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -416,7 +416,7 @@
         <v>11.39450537313996</v>
       </c>
       <c r="D2">
-        <v>1804.902889521739</v>
+        <v>1674.834856090909</v>
       </c>
       <c r="E2">
         <v>2.203141217391304</v>
@@ -454,7 +454,7 @@
         <v>1710.125593666666</v>
       </c>
       <c r="E3">
-        <v>36.93787716666667</v>
+        <v>32.42262530434783</v>
       </c>
       <c r="F3">
         <v>35.70891577502608</v>
@@ -486,7 +486,7 @@
         <v>8.201270391644965</v>
       </c>
       <c r="D4">
-        <v>2003.984436130434</v>
+        <v>1898.268088954545</v>
       </c>
       <c r="E4">
         <v>1.953695304347826</v>
@@ -521,7 +521,7 @@
         <v>5.739018238132328</v>
       </c>
       <c r="D5">
-        <v>1887.188372521739</v>
+        <v>1764.405060681818</v>
       </c>
       <c r="E5">
         <v>29.7024464347826</v>
@@ -556,7 +556,7 @@
         <v>7.655831792183652</v>
       </c>
       <c r="D6">
-        <v>2212.912478416666</v>
+        <v>1742.271460652174</v>
       </c>
       <c r="E6">
         <v>3.652091083333334</v>
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C7">
-        <v>28.10353263719835</v>
+        <v>27.29010847939239</v>
       </c>
       <c r="D7">
-        <v>2324.555826173913</v>
+        <v>2094.896802047619</v>
       </c>
       <c r="E7">
-        <v>74.63134674999999</v>
+        <v>57.7643998</v>
       </c>
       <c r="F7">
         <v>57.02046334501584</v>
@@ -623,13 +623,13 @@
         </is>
       </c>
       <c r="C8">
-        <v>62.09433203544391</v>
+        <v>44.5836127478705</v>
       </c>
       <c r="D8">
         <v>2041.166549999999</v>
       </c>
       <c r="E8">
-        <v>44.21823577777777</v>
+        <v>35.95150599999999</v>
       </c>
       <c r="F8">
         <v>0.6193626878108659</v>
@@ -699,7 +699,7 @@
         <v>2310.263845333333</v>
       </c>
       <c r="E10">
-        <v>59.68061308333333</v>
+        <v>26.35060666666666</v>
       </c>
       <c r="F10">
         <v>30.71642797014066</v>
@@ -731,10 +731,10 @@
         <v>7.383954549439532</v>
       </c>
       <c r="D11">
-        <v>2096.08183725</v>
+        <v>2011.743463304348</v>
       </c>
       <c r="E11">
-        <v>30.4560095</v>
+        <v>26.39412078260869</v>
       </c>
       <c r="F11">
         <v>14.64202951297203</v>
@@ -763,13 +763,13 @@
         </is>
       </c>
       <c r="C12">
-        <v>25.14029964691035</v>
+        <v>19.67582970411651</v>
       </c>
       <c r="D12">
-        <v>2438.210254458333</v>
+        <v>2241.871540954545</v>
       </c>
       <c r="E12">
-        <v>97.52924883333333</v>
+        <v>41.54455569230769</v>
       </c>
       <c r="F12">
         <v>24.66607317524519</v>
@@ -929,31 +929,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="C17">
-        <v>15.95241560479417</v>
+        <v>6.445262083285449</v>
       </c>
       <c r="D17">
-        <v>1255.628657631579</v>
+        <v>780.7548054666665</v>
       </c>
       <c r="E17">
-        <v>185.23714075</v>
+        <v>14.335073875</v>
       </c>
       <c r="F17">
-        <v>41.88614063004911</v>
+        <v>13.9804475854801</v>
       </c>
       <c r="G17">
-        <v>54.90499817969565</v>
+        <v>85.11655118149527</v>
       </c>
       <c r="H17">
-        <v>3.208861190255248</v>
+        <v>0.9030012330246364</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -969,30 +969,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C18">
-        <v>6.445262083285449</v>
+        <v>35.69871494787759</v>
       </c>
       <c r="D18">
-        <v>780.7548054666665</v>
+        <v>631.0621599999999</v>
       </c>
       <c r="E18">
-        <v>14.335073875</v>
+        <v>2.06036</v>
       </c>
       <c r="F18">
-        <v>13.9804475854801</v>
+        <v>2.826438092271004</v>
       </c>
       <c r="G18">
-        <v>85.11655118149527</v>
+        <v>65.39762244774417</v>
       </c>
       <c r="H18">
-        <v>0.9030012330246364</v>
+        <v>31.77593945998482</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>NI</t>
         </is>
       </c>
     </row>
@@ -1004,30 +1004,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>JL</t>
         </is>
       </c>
       <c r="C19">
-        <v>51.24670738429023</v>
+        <v>7.757467649992235</v>
       </c>
       <c r="D19">
-        <v>631.0621599999999</v>
+        <v>386.3586859166667</v>
       </c>
       <c r="E19">
-        <v>2.06036</v>
+        <v>0.2165184999999995</v>
       </c>
       <c r="F19">
-        <v>2.826438092271004</v>
+        <v>5.515947190542528</v>
       </c>
       <c r="G19">
-        <v>65.39762244774417</v>
+        <v>92.85765957737357</v>
       </c>
       <c r="H19">
-        <v>31.77593945998482</v>
+        <v>1.626393232083907</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>NI</t>
+          <t>MI</t>
         </is>
       </c>
     </row>
@@ -1039,26 +1039,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="C20">
-        <v>7.757467649992235</v>
+        <v>35.69660358205611</v>
       </c>
       <c r="D20">
-        <v>386.3586859166667</v>
+        <v>197.119718</v>
       </c>
       <c r="E20">
-        <v>0.2165184999999995</v>
+        <v>66.0513772</v>
       </c>
       <c r="F20">
-        <v>5.515947190542528</v>
+        <v>27.38153042957602</v>
       </c>
       <c r="G20">
-        <v>92.85765957737357</v>
+        <v>61.73465697431114</v>
       </c>
       <c r="H20">
-        <v>1.626393232083907</v>
+        <v>10.88381259611284</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1069,35 +1069,35 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>September</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="C21">
-        <v>44.42855889581177</v>
+        <v>11.15822702562157</v>
       </c>
       <c r="D21">
-        <v>197.119718</v>
+        <v>45.10045320833332</v>
       </c>
       <c r="E21">
-        <v>80.88216575</v>
+        <v>3.415001874999999</v>
       </c>
       <c r="F21">
-        <v>27.38153042957602</v>
+        <v>0.131464580617123</v>
       </c>
       <c r="G21">
-        <v>61.73465697431114</v>
+        <v>75.48390292973056</v>
       </c>
       <c r="H21">
-        <v>10.88381259611284</v>
+        <v>24.38463248965232</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>NI</t>
         </is>
       </c>
     </row>
@@ -1109,30 +1109,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BC</t>
+          <t>BL</t>
         </is>
       </c>
       <c r="C22">
-        <v>11.15822702562157</v>
+        <v>8.233454415029239</v>
       </c>
       <c r="D22">
-        <v>45.10045320833332</v>
+        <v>250.2943524583333</v>
       </c>
       <c r="E22">
-        <v>3.415001874999999</v>
+        <v>1.185580875</v>
       </c>
       <c r="F22">
-        <v>0.131464580617123</v>
+        <v>57.23747644727604</v>
       </c>
       <c r="G22">
-        <v>75.48390292973056</v>
+        <v>40.84547567360879</v>
       </c>
       <c r="H22">
-        <v>24.38463248965232</v>
+        <v>1.917047879115174</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>NI</t>
+          <t>MI</t>
         </is>
       </c>
     </row>
@@ -1144,30 +1144,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BL</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="C23">
-        <v>8.233454415029239</v>
+        <v>12.20816760869288</v>
       </c>
       <c r="D23">
-        <v>250.2943524583333</v>
+        <v>179.4250613043478</v>
       </c>
       <c r="E23">
-        <v>1.185580875</v>
+        <v>10.793039</v>
       </c>
       <c r="F23">
-        <v>57.23747644727604</v>
+        <v>0.5153987371392847</v>
       </c>
       <c r="G23">
-        <v>40.84547567360879</v>
+        <v>73.07064078837615</v>
       </c>
       <c r="H23">
-        <v>1.917047879115174</v>
+        <v>26.41396047448456</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>NI</t>
         </is>
       </c>
     </row>
@@ -1179,63 +1179,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CC</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="C24">
-        <v>12.20816760869288</v>
+        <v>4.058007587025487</v>
       </c>
       <c r="D24">
-        <v>397.57272775</v>
+        <v>74.03820191304347</v>
       </c>
       <c r="E24">
-        <v>10.793039</v>
+        <v>3.672054874999999</v>
       </c>
       <c r="F24">
-        <v>0.5153987371392847</v>
+        <v>33.63866472399008</v>
       </c>
       <c r="G24">
-        <v>73.07064078837615</v>
+        <v>65.07685587737755</v>
       </c>
       <c r="H24">
-        <v>26.41396047448456</v>
+        <v>1.284479398632361</v>
       </c>
       <c r="I24" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>September</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="C25">
-        <v>4.058007587025487</v>
-      </c>
-      <c r="D25">
-        <v>74.03820191304347</v>
-      </c>
-      <c r="E25">
-        <v>3.672054874999999</v>
-      </c>
-      <c r="F25">
-        <v>33.63866472399008</v>
-      </c>
-      <c r="G25">
-        <v>65.07685587737755</v>
-      </c>
-      <c r="H25">
-        <v>1.284479398632361</v>
-      </c>
-      <c r="I25" t="inlineStr">
         <is>
           <t>MI</t>
         </is>
